--- a/output/pdf_financials_xlsx/TRG.xlsx
+++ b/output/pdf_financials_xlsx/TRG.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.159179</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.131614</v>
       </c>
     </row>
     <row r="13">
@@ -786,10 +786,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.281123</v>
+        <v>-0.440302</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.420809</v>
+        <v>0.289195</v>
       </c>
     </row>
     <row r="28">
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.281123</v>
+        <v>-0.440302</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.420809</v>
+        <v>0.289195</v>
       </c>
     </row>
     <row r="30">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">

--- a/output/pdf_financials_xlsx/TRG.xlsx
+++ b/output/pdf_financials_xlsx/TRG.xlsx
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>0</v>
+        <v>-0.11073</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0.00412</v>
@@ -690,11 +690,15 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>-0.281123</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>0.420809</v>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -704,10 +708,10 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>0.042138</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-0.061701</v>
       </c>
     </row>
     <row r="22">
@@ -1742,10 +1746,10 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>-0.14113</v>
+        <v>-0.281123</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>-0.281123</v>
+        <v>0.420809</v>
       </c>
     </row>
     <row r="100">
@@ -1833,7 +1837,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.032279</v>
+        <v>-0.074014</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>-0.005625</v>
@@ -1989,7 +1993,7 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-1.708478</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0</v>
@@ -2231,7 +2235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3164,7 +3168,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>-0.281123</v>
       </c>
@@ -3729,206 +3737,210 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>OPERATING ACTIVITIES</t>
+        </is>
+      </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Note July 31, 2025 July</t>
+          <t>Net loss for the year (281,123)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>-17.776096</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Consulting fees 7</t>
+          <t>Stock-based compensation 7 139,213</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>0.05663</v>
-      </c>
-      <c r="F56" s="5" t="n">
-        <v>0.052812</v>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>General and administrative costs</t>
+          <t>Loss on sale of assets 5 -</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" s="5" t="n">
-        <v>0.114461</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>0.087961</v>
+        <v>8.959776</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Loss on control of subsidiary 5 -</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" s="5" t="n">
-        <v>0.015653</v>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>0.014811</v>
+        <v>1.122311</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Management fees 7</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Impairment loss on write-off exploration and evaluation assets 6 -</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" s="5" t="n">
-        <v>0.052278</v>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>0.1061</v>
+        <v>6.714329</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Change in tax and other receivable (14,621)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" s="5" t="n">
-        <v>0.055729</v>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>0.049625</v>
+        <v>1.193668</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Shareholder information and investor relations</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Changes in consideration receivable 993,092</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" s="5" t="n">
-        <v>0.008758999999999999</v>
-      </c>
-      <c r="F61" s="5" t="n">
-        <v>0.004405</v>
+        <v>-0.993092</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Stock-based compensation 6(b)</t>
+          <t>Change in prepaid expenses (3,698)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" s="5" t="n">
-        <v>0.139213</v>
+        <v>1.038286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3939,238 +3951,246 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Change in accounts payable and accrued liabilities (13,960)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" s="5" t="n">
-        <v>0.039717</v>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>0.04404</v>
+        <v>-0.333196</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TOTAL OPERATING EXPENSES</t>
+          <t>Changes in non-cash working capital items total</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>ChangeInWorkingCapital</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0.48244</v>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>0.359754</v>
+        <v>-0.074014</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Exploration and evaluation assets - expenditures 6 -</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0.159179</v>
-      </c>
-      <c r="F65" s="5" t="n">
-        <v>0.131614</v>
+        <v>-1.708478</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>0.00412</v>
+          <t>Exploration and evaluation assets - proceeds of sale of assets 6 -</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" s="5" t="n">
+        <v>3.5025</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Gain on sale of subsidiary 5(a)</t>
+          <t>Short-term investment 3 (866,935)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" s="5" t="n">
-        <v>0.70653</v>
+      <c r="E67" s="5" t="n">
+        <v>-2.24009</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>INCOME (LOSS) FROM CONTINUING OPERATIONS</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>INVESTING ACTIVITIES total</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E68" s="5" t="n">
-        <v>-0.323261</v>
-      </c>
-      <c r="F68" s="5" t="n">
-        <v>0.48251</v>
+        <v>-0.446068</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Net income (loss) for discontinued operations 5</t>
+          <t>NET CHANGE IN CASH (48,032)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" s="5" t="n">
-        <v>0.042138</v>
-      </c>
-      <c r="F69" s="5" t="n">
-        <v>-0.061701</v>
+        <v>-0.520082</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NET INCOME (LOSS) FOR THE YEAR</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Effects of exchange rate fluctuation on cash 139,993</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" s="5" t="n">
-        <v>-0.281123</v>
-      </c>
-      <c r="F70" s="5" t="n">
-        <v>0.420809</v>
+        <v>0.201602</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Item that will be reclassified subsequently to loss</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Unrealized gain on foreign exchange translation</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>CASH, BEGINNING OF THE YEAR 194,303</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E71" s="5" t="n">
-        <v>0.139993</v>
+        <v>0.512783</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -4181,81 +4201,1355 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Item that will be reclassified subsequently to loss</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>COMPEHENSIVE INCOME (LOSS) FOR THE YEAR</t>
+          <t>CASH, END OF THE YEAR 286,264</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>-0.14113</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>0.420809</v>
+        <v>0.194303</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Item that will be reclassified subsequently to loss</t>
+          <t>Supplemental cash information</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>INCOME (LOSS) PER SHARE (basic and diluted)</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Shares issued for E&amp;E acquisition -</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OUTSTANDING</t>
+          <t>Balance, July 31, 2022 118,251,810 24,166,857 3,346,883 5,863 (6,729,981)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" s="5" t="n">
+        <v>20.789622</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Shares issued - exploration and evaluation assets 1,000,000 70,000 - - -</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year - - - 320,538 (17,776,096)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" s="5" t="n">
+        <v>-17.455558</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Balance, July 31, 2023 119,251,810 24,236,857 3,346,883 326,401 (24,506,077)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" s="5" t="n">
+        <v>3.404064</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Stock-based compensation - - 139,213 - -</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" s="5" t="n">
+        <v>0.139213</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year - - - 139,993 (281,123)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" s="5" t="n">
+        <v>-0.14113</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Balance, July 31, 2024 119,251,810 24,236,857 3,486,096 466,394 (24,787,200)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" s="5" t="n">
+        <v>3.402147</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Note July 31, 2025 July</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" s="5" t="n">
+        <v>0.002024</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Consulting fees 7</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>0.05663</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>0.052812</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>General and administrative costs</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" s="5" t="n">
+        <v>0.114461</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>0.087961</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>0.015653</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>0.014811</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Management fees 7</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>0.052278</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>0.1061</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>0.055729</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>0.049625</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Shareholder information and investor relations</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>0.008758999999999999</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>0.004405</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Stock-based compensation 6(b)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" s="5" t="n">
+        <v>0.139213</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>0.039717</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>0.04404</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>TOTAL OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>0.48244</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>0.359754</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>0.159179</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>0.131614</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>0.00412</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Gain on sale of subsidiary 5(a)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>0.70653</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>INCOME (LOSS) FROM CONTINUING OPERATIONS</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" s="5" t="n">
+        <v>-0.323261</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>0.48251</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Net income (loss) for discontinued operations 5</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>0.042138</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>-0.061701</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>NET INCOME (LOSS) FOR THE YEAR</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>-0.281123</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>0.420809</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Item that will be reclassified subsequently to loss</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Unrealized gain on foreign exchange translation</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" s="5" t="n">
+        <v>0.139993</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Item that will be reclassified subsequently to loss</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>COMPEHENSIVE INCOME (LOSS) FOR THE YEAR</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>-0.14113</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>0.420809</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Item that will be reclassified subsequently to loss</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>INCOME (LOSS) PER SHARE (basic and diluted)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>OUTSTANDING</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" s="5" t="n">
         <v>119.25181</v>
       </c>
-      <c r="F74" s="5" t="n">
+      <c r="F100" s="5" t="n">
         <v>119.25181</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Consulting fees 8 56,630</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>0.203286</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>General and administrative costs 114,461</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" s="5" t="n">
+        <v>0.200052</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Insurance 15,653</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="n">
+        <v>0.052551</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Management fees 8 52,278</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>0.133819</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Professional fees 55,729</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>0.112054</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Shareholder information and investor relations 8,759</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>0.153785</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Stock-based compensation 7 139,213</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Transfer agent and filing fees 39,717</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>0.045482</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Total operating expenses (482,440)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" s="5" t="n">
+        <v>-0.901029</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss -</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>-0.11073</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Interest income 159,179</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>0.011306</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Loss on sale of assets 5 -</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" s="5" t="n">
+        <v>-8.959776</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Loss on control of subsidiary 5 -</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" s="5" t="n">
+        <v>-1.139964</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Impairment loss on write off exploration and evaluation assets 6 -</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" s="5" t="n">
+        <v>-6.714329</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>LOSS FROM CONTINUING OPERATIONS (159,179)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" s="5" t="n">
+        <v>-17.814522</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Net gain for discontinued operations 42,138</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" s="5" t="n">
+        <v>0.038426</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>NET LOSS FOR THE YEAR (281,123)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" s="5" t="n">
+        <v>-17.776096</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Item that will be reclassified subsequently to loss</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Unrealized gain on foreign exchange translation 139,993</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" s="5" t="n">
+        <v>0.320538</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Item that will be reclassified subsequently to loss</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>NET AND COMPEHENSIVE LOSS FOR THE YEAR (141,130)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" s="5" t="n">
+        <v>-17.455558</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Item that will be reclassified subsequently to loss</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>LOSS PER SHARE (basic and diluted) (0.00)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" s="5" t="n">
+        <v>-1.5e-07</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>(basic and diluted) 119,251,810</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" s="5" t="n">
+        <v>119.068248</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>
